--- a/test/lix/outputs/li_halides_gbci_grad_fd_sweep.xlsx
+++ b/test/lix/outputs/li_halides_gbci_grad_fd_sweep.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -550,22 +550,22 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.01830102797348371</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.01830105662525838</v>
+        <v>0.0183010566243702</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-2.865177467503699e-08</v>
+        <v>-2.865091336401449e-08</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.865177467503699e-08</v>
+        <v>2.865091336401449e-08</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.864955423177384e-08</v>
+        <v>2.864913706224557e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9999804052547736</v>
+        <v>0.9999804052547727</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-0.01830102797348387</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>-0.01830105662081749</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.864733361640504e-08</v>
+        <v>2.864736065033568e-08</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.865177467503699e-08</v>
+        <v>2.865091336401449e-08</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.864955423177384e-08</v>
+        <v>2.864913706224557e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9999804052547736</v>
+        <v>0.9999804052547727</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.01830102797348371</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.01830103513089654</v>
+        <v>0.018301035128232</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-7.157412829084109e-09</v>
+        <v>-7.154775161222204e-09</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7.157412829084109e-09</v>
+        <v>7.158327874901005e-09</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.156524622522821e-09</v>
+        <v>7.156551738519989e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9999902094054244</v>
+        <v>0.9999902094054227</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -697,22 +697,22 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-0.01830102797348387</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0.01830103512912018</v>
+        <v>-0.01830103513178472</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.155636305711255e-09</v>
+        <v>7.158327874901005e-09</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>7.157412829084109e-09</v>
+        <v>7.158327874901005e-09</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.156524622522821e-09</v>
+        <v>7.156551738519989e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9999902094054244</v>
+        <v>0.9999902094054227</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.01830102797348371</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.01830102829281088</v>
+        <v>0.01830102911659637</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-3.193271758128446e-10</v>
+        <v>-1.143139527481907e-09</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3.193271758128446e-10</v>
+        <v>1.147580419580407e-09</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.840984100345884e-10</v>
+        <v>1.145362125857124e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9999980429658295</v>
+        <v>0.9999960853892442</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -795,22 +795,22 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>-0.01830102797348387</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0.01830102821731572</v>
+        <v>-0.01830102912103726</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.438318436048803e-10</v>
+        <v>1.147580419580407e-09</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3.193271758128446e-10</v>
+        <v>1.147580419580407e-09</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2.840984100345884e-10</v>
+        <v>1.145362125857124e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9999980429658295</v>
+        <v>0.9999960853892442</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -844,28 +844,24 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.01830102797348371</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.0183010279464213</v>
+        <v>0.01830102826172464</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.70624078702042e-11</v>
+        <v>-2.882677985205362e-10</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4.399169917235213e-11</v>
+        <v>3.060313669145387e-10</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3.652152458348376e-11</v>
+        <v>2.972822910967432e-10</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9999990215507203</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.9999980429658305</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -886,7 +882,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -897,28 +893,24 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>-0.01830102797348387</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0.01830102801747557</v>
+        <v>-0.01830102827948821</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.399169917235213e-11</v>
+        <v>3.060313669145387e-10</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4.399169917235213e-11</v>
+        <v>3.060313669145387e-10</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3.652152458348376e-11</v>
+        <v>2.972822910967432e-10</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9999990215507203</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.9999980429658305</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -939,7 +931,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -950,22 +942,22 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.01830102797348371</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.01830102802635736</v>
+        <v>0.01830102805300271</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-5.287364990280707e-11</v>
+        <v>-7.954586989100676e-11</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>8.03532795856654e-11</v>
+        <v>7.954586989100676e-11</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.801570551797843e-11</v>
+        <v>5.624810069371338e-11</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9999998043209934</v>
+        <v>0.9999990215507195</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -988,7 +980,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -999,22 +991,22 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-0.01830102797348387</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0.01830102789313059</v>
+        <v>-0.01830102797306665</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-8.03532795856654e-11</v>
+        <v>-3.901878820045113e-13</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>8.03532795856654e-11</v>
+        <v>7.954586989100676e-11</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.801570551797843e-11</v>
+        <v>5.624810069371338e-11</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9999998043209934</v>
+        <v>0.9999990215507195</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1022,22 +1014,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LiF</t>
+          <t>LiH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3,4,7,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.001</v>
+        <v>2e-05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1048,94 +1040,102 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.03524757630657405</v>
+        <v>0.01830102798194844</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-1.330913033115166e-07</v>
+        <v>-8.491596314996741e-12</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.330913033115166e-07</v>
+        <v>3.591732467000952e-11</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1.330735473671581e-07</v>
+        <v>2.609752305706176e-11</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9999783088580543</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>0.9999996086365615</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LiF</t>
+          <t>LiH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3,4,7,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.001</v>
+        <v>2e-05</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0.03524757627104691</v>
+        <v>-0.01830102793753952</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.330557890533157e-07</v>
+        <v>-3.591732467000952e-11</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.330913033115166e-07</v>
+        <v>3.591732467000952e-11</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1.330735473671581e-07</v>
+        <v>2.609752305706176e-11</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9999783088580543</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>0.9999996086365615</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LiF</t>
+          <t>LiH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3,4,7,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0005</v>
+        <v>1e-05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1146,22 +1146,22 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.03524747631900027</v>
+        <v>0.01830102771549491</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-3.310372953535534e-08</v>
+        <v>2.579619295950408e-10</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3.310372953535534e-08</v>
+        <v>2.579619295950408e-10</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3.308242655587926e-08</v>
+        <v>1.910453648501145e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9999891630406558</v>
+        <v>0.9999998043209929</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1169,48 +1169,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LiF</t>
+          <t>LiH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3,4,7,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.0005</v>
+        <v>1e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-0.03524747627636771</v>
+        <v>-0.01830102789313059</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.306110984979682e-08</v>
+        <v>-8.032624565501578e-11</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3.310372953535534e-08</v>
+        <v>2.579619295950408e-10</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3.308242655587926e-08</v>
+        <v>1.910453648501145e-10</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9999891630406558</v>
+        <v>0.9999998043209929</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.03524744450089656</v>
+        <v>0.03524757631367947</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-1.285625828018055e-09</v>
+        <v>-1.330884948913535e-07</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.783018621637211e-09</v>
+        <v>1.331737706777858e-07</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.554346997097522e-09</v>
+        <v>1.331311396123862e-07</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9999978339853581</v>
+        <v>0.9999783088580678</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0.03524744499827648</v>
+        <v>-0.0352475763989446</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.783018621637211e-09</v>
+        <v>1.331737706777858e-07</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.783018621637211e-09</v>
+        <v>1.331737706777858e-07</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.554346997097522e-09</v>
+        <v>1.331311396123862e-07</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9999978339853581</v>
+        <v>0.9999783088580678</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0005</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1342,28 +1342,24 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.03524744499827648</v>
+        <v>0.03524747619110258</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-1.783005743050126e-09</v>
+        <v>-3.296591799539783e-08</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.783005743050126e-09</v>
+        <v>3.306540463654528e-08</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.269202930710377e-09</v>
+        <v>3.301569878904401e-08</v>
       </c>
       <c r="M18" t="n">
-        <v>0.999998917078736</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.9999891630406625</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1384,7 +1380,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0005</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1395,28 +1391,24 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0.03524744300875682</v>
+        <v>-0.03524747629057856</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-2.065010384910693e-10</v>
+        <v>3.306540463654528e-08</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.783005743050126e-09</v>
+        <v>3.306540463654528e-08</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.269202930710377e-09</v>
+        <v>3.301569878904401e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>0.999998917078736</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.9999891630406625</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1437,7 +1429,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1e-05</v>
+        <v>0.0002</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1448,22 +1440,22 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.0352474465614705</v>
+        <v>0.03524744812466452</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-3.346199761722346e-09</v>
+        <v>-4.899479932873874e-09</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4.767298111829632e-09</v>
+        <v>5.006072001378925e-09</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.118506047853096e-09</v>
+        <v>4.953062713898532e-09</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9999997834295158</v>
+        <v>0.9999956672822105</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1486,7 +1478,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1e-05</v>
+        <v>0.0002</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1497,22 +1489,22 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-0.03524744798255597</v>
+        <v>-0.03524744823124593</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4.767298111829632e-09</v>
+        <v>5.006072001378925e-09</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4.767298111829632e-09</v>
+        <v>5.006072001378925e-09</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.118506047853096e-09</v>
+        <v>4.953062713898532e-09</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9999997834295158</v>
+        <v>0.9999956672822105</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1520,7 +1512,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1531,11 +1523,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1546,22 +1538,22 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.3397178301725035</v>
+        <v>0.0352474452114393</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-2.336066735608711e-07</v>
+        <v>-1.986254716257463e-09</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.337204341174015e-07</v>
+        <v>1.986254716257463e-09</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2.336635607622656e-07</v>
+        <v>1.916523180310483e-09</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9998816702115469</v>
+        <v>0.9999978339853591</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1569,7 +1561,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1580,37 +1572,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0.3397178302861903</v>
+        <v>-0.03524744506933075</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.337204341174015e-07</v>
+        <v>1.844156827246479e-09</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2.337204341174015e-07</v>
+        <v>1.986254716257463e-09</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2.336635607622656e-07</v>
+        <v>1.916523180310483e-09</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9998816702115469</v>
+        <v>0.9999978339853591</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1618,7 +1610,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1629,11 +1621,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.0005</v>
+        <v>5e-05</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1644,30 +1636,34 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.3397176548673997</v>
+        <v>0.03524744329297391</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-5.830156979413914e-08</v>
+        <v>-6.778932970519236e-11</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5.830156979413914e-08</v>
+        <v>1.062559817910369e-09</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>5.82731918572385e-08</v>
+        <v>7.528707591146026e-10</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9999408486791898</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>0.9999989170787364</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1678,45 +1674,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.0005</v>
+        <v>5e-05</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-0.3397176548105563</v>
+        <v>-0.03524744428773374</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.824480009408717e-08</v>
+        <v>1.062559817910369e-09</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5.830156979413914e-08</v>
+        <v>1.062559817910369e-09</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>5.82731918572385e-08</v>
+        <v>7.528707591146026e-10</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9999408486791898</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>0.9999989170787364</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1727,11 +1727,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.0001</v>
+        <v>2e-05</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1742,34 +1742,30 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.3397175987629453</v>
+        <v>0.0352474376796863</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-2.19711537852163e-09</v>
+        <v>5.545498282799599e-09</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3.334057474546626e-09</v>
+        <v>6.611301728298713e-09</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2.823407093399433e-09</v>
+        <v>6.10171540417688e-09</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9999881719069121</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.999999566852147</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1780,49 +1776,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.0001</v>
+        <v>2e-05</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-0.3397175998998136</v>
+        <v>-0.0352474366138722</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.334057474546626e-09</v>
+        <v>-6.611301728298713e-09</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3.334057474546626e-09</v>
+        <v>6.611301728298713e-09</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2.823407093399433e-09</v>
+        <v>6.10171540417688e-09</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9999881719069121</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.999999566852147</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1833,11 +1825,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1848,22 +1840,22 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.03524744322518458</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.3397175959207743</v>
+        <v>0.03524744371929955</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6.450555645187706e-10</v>
+        <v>-4.941149711612525e-10</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3.902491663154706e-09</v>
+        <v>1.204668365062389e-09</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2.796921330884068e-09</v>
+        <v>9.206995912097971e-10</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9999940860891267</v>
+        <v>0.9999997834295155</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1871,7 +1863,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LiCl</t>
+          <t>LiF</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1882,37 +1874,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7,8,11,14</t>
+          <t>3,4,7,10</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.03524744322517392</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-0.3397176004682478</v>
+        <v>-0.03524744442984229</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3.902491663154706e-09</v>
+        <v>1.204668365062389e-09</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3.902491663154706e-09</v>
+        <v>1.204668365062389e-09</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2.796921330884068e-09</v>
+        <v>9.206995912097971e-10</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9999940860891267</v>
+        <v>0.9999997834295155</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1935,7 +1927,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1e-05</v>
+        <v>0.001</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1946,22 +1938,22 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.3397175965682662</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.3397176243424837</v>
+        <v>0.3397178302861903</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-2.777665381037409e-08</v>
+        <v>-2.337179241251874e-07</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.777665381037409e-08</v>
+        <v>2.337179241251874e-07</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2.10539815559692e-08</v>
+        <v>2.335758943132801e-07</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9999988172395315</v>
+        <v>0.9998816702115806</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1984,7 +1976,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1e-05</v>
+        <v>0.001</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -1995,25 +1987,621 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.3397175965681951</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-0.339717607289458</v>
+        <v>-0.3397178300019732</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.072370187094052e-08</v>
+        <v>2.33433778085157e-07</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.777665381037409e-08</v>
+        <v>2.337179241251874e-07</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2.10539815559692e-08</v>
+        <v>2.335758943132801e-07</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9999988172395315</v>
+        <v>0.9998816702115806</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.3397176548673997</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>-5.82991335207339e-08</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>5.869710850703314e-08</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>5.84984594513171e-08</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.9999408486792066</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cl</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-0.3397176552653036</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>5.869710850703314e-08</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>5.869710850703314e-08</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>5.84984594513171e-08</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9999408486792066</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0.3397176055841555</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>-9.015889368413355e-09</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>9.015889368413355e-09</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>8.736331054250387e-09</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.9999763427284053</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cl</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-0.3397176050157213</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>8.44752623407885e-09</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>9.015889368413355e-09</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>8.736331054250387e-09</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9999763427284053</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.3397175981945111</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>-1.626244916508313e-09</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1.626244916508313e-09</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>1.490956391500474e-09</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.9999881719069152</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cl</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-0.339717597910294</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1.342098876477849e-09</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1.626244916508313e-09</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1.490956391500474e-09</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.9999881719069152</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0.339717594783906</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1.784360215140168e-09</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>2.194750159389969e-09</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>2.00010870198564e-09</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.9999940860891284</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cl</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-0.3397175987629453</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>2.194750159389969e-09</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2.194750159389969e-09</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>2.00010870198564e-09</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.9999940860891284</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0.3397176001840307</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>-3.615764521125442e-09</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>3.615764521125442e-09</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>2.945545062425617e-09</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.9999976344682114</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cl</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-0.3397175944996888</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>-2.068506310681784e-09</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>3.615764521125442e-09</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>2.945545062425617e-09</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9999976344682114</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0.3397175873942614</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>9.174004722556361e-09</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>9.174004722556361e-09</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>7.8820549940436e-09</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9999988172395318</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7,8,11,14</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cl</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-0.3397175902364324</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>-6.331762725242385e-09</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>9.174004722556361e-09</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>7.8820549940436e-09</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9999988172395318</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2026,496 +2614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>setting</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>basis</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ccpvdz</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bond length (Angstrom)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ncas</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>nelecas</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>act_list (1-based)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>act_list character</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2: sigma(Li2s/2pz-H1s); 3: sigma*(Li3s/3pz). Same as the default window for this molecule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>reference energy (Eh)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-7.981843552641519</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>net force norm (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.665334536937735e-16</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>torque (Eh)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.985102716948732e-18</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>atom</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>analytic z (Eh/bohr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Li</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.01830102797348371</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>-0.01830102797348387</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>step_bohr</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>analytic z Li (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>numerical z Li (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>diff Li (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>analytic z H (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>numerical z H (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>diff H (Eh/bohr)</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>max_abs_error_Eh_per_bohr</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>rms_error_Eh_per_bohr</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>min_active_overlap</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>best_step</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0.01830102797348371</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0.01830105662525838</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>-2.865177467503699e-08</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-0.01830102797348387</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-0.01830105662081749</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>2.864733361640504e-08</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>2.865177467503699e-08</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>2.864955423177384e-08</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.9999804052547736</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0.01830102797348371</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0.01830103513089654</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>-7.157412829084109e-09</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>-0.01830102797348387</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-0.01830103512912018</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>7.155636305711255e-09</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>7.157412829084109e-09</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>7.156524622522821e-09</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.9999902094054244</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.01830102797348371</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0.01830102829281088</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>-3.193271758128446e-10</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>-0.01830102797348387</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-0.01830102821731572</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>2.438318436048803e-10</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>3.193271758128446e-10</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>2.840984100345884e-10</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.9999980429658295</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0.01830102797348371</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0.0183010279464213</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>2.70624078702042e-11</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>-0.01830102797348387</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-0.01830102801747557</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>4.399169917235213e-11</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>4.399169917235213e-11</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>3.652152458348376e-11</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.9999990215507203</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0.01830102797348371</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0.01830102802635736</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>-5.287364990280707e-11</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-0.01830102797348387</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-0.01830102789313059</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>-8.03532795856654e-11</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>8.03532795856654e-11</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>6.801570551797843e-11</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9999998043209934</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h from (bohr)</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>h to (bohr)</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>log-log slope</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-0.3743120141505509</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>near the optimum</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>2.859732105013378</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>truncation (h^2), step too large</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>1.932157573285997</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>truncation (h^2), step too large</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>2.00111440177753</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>truncation (h^2), step too large</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2572,7 +2671,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2582,7 +2681,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2593,7 +2692,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[3, 4, 7, 10]</t>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2704,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3: sigma(F2s); 4: sigma(F2pz-Li); 7: sigma*(Li3s); 10: sigma*(Li3pz).  Default window would be [5,6,7,8], whose MOs 5 and 6 are the F 2p pi lone pairs.</t>
+          <t>2: sigma(Li2s/2pz-H1s); 3: sigma*(Li3s/3pz). Same as the default window for this molecule.</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-106.9430017857987</v>
+        <v>-7.981843552641483</v>
       </c>
     </row>
     <row r="9">
@@ -2626,7 +2725,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.287858708565182e-14</v>
+        <v>2.393118111723986e-31</v>
       </c>
     </row>
     <row r="10">
@@ -2636,7 +2735,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.031412193831128e-16</v>
+        <v>3.296923197929545e-17</v>
       </c>
     </row>
     <row r="11"/>
@@ -2659,17 +2758,17 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
     </row>
     <row r="15"/>
@@ -2696,17 +2795,17 @@
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>analytic z F (Eh/bohr)</t>
+          <t>analytic z H (Eh/bohr)</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>numerical z F (Eh/bohr)</t>
+          <t>numerical z H (Eh/bohr)</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>diff F (Eh/bohr)</t>
+          <t>diff H (Eh/bohr)</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
@@ -2735,31 +2834,31 @@
         <v>0.001</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.03524757630657405</v>
+        <v>0.0183010566243702</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-1.330913033115166e-07</v>
+        <v>-2.865091336401449e-08</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.03524757627104691</v>
+        <v>-0.01830105662081749</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.330557890533157e-07</v>
+        <v>2.864736065033568e-08</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.330913033115166e-07</v>
+        <v>2.865091336401449e-08</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.330735473671581e-07</v>
+        <v>2.864913706224557e-08</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9999783088580543</v>
+        <v>0.9999804052547727</v>
       </c>
       <c r="K17" t="inlineStr"/>
     </row>
@@ -2768,226 +2867,911 @@
         <v>0.0005</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.03524747631900027</v>
+        <v>0.018301035128232</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-3.310372953535534e-08</v>
+        <v>-7.154775161222204e-09</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-0.03524747627636771</v>
+        <v>-0.01830103513178472</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3.306110984979682e-08</v>
+        <v>7.158327874901005e-09</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.310372953535534e-08</v>
+        <v>7.158327874901005e-09</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3.308242655587926e-08</v>
+        <v>7.156551738519989e-09</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9999891630406558</v>
+        <v>0.9999902094054227</v>
       </c>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.03524744450089656</v>
+        <v>0.01830102911659637</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-1.285625828018055e-09</v>
+        <v>-1.143139527481907e-09</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.03524744499827648</v>
+        <v>-0.01830102912103726</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.783018621637211e-09</v>
+        <v>1.147580419580407e-09</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.783018621637211e-09</v>
+        <v>1.147580419580407e-09</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.554346997097522e-09</v>
+        <v>1.145362125857124e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9999978339853581</v>
+        <v>0.9999960853892442</v>
       </c>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.03524744321527074</v>
+        <v>0.01830102797345684</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.03524744499827648</v>
+        <v>0.01830102826172464</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-1.783005743050126e-09</v>
+        <v>-2.882677985205362e-10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.03524744321525786</v>
+        <v>-0.01830102797345684</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.03524744300875682</v>
+        <v>-0.01830102827948821</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-2.065010384910693e-10</v>
+        <v>3.060313669145387e-10</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.783005743050126e-09</v>
+        <v>3.060313669145387e-10</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.269202930710377e-09</v>
+        <v>2.972822910967432e-10</v>
       </c>
       <c r="J20" t="n">
-        <v>0.999998917078736</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.9999980429658305</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.01830102797345684</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0.01830102805300271</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-7.954586989100676e-11</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-0.01830102797345684</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-0.01830102797306665</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>-3.901878820045113e-13</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>7.954586989100676e-11</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>5.624810069371338e-11</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9999990215507195</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.01830102797345684</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0.01830102798194844</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>-8.491596314996741e-12</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-0.01830102797345684</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-0.01830102793753952</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-3.591732467000952e-11</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>3.591732467000952e-11</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>2.609752305706176e-11</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9999996086365615</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>1e-05</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>0.03524744321527074</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0.0352474465614705</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>-3.346199761722346e-09</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-0.03524744321525786</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-0.03524744798255597</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>4.767298111829632e-09</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>4.767298111829632e-09</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>4.118506047853096e-09</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9999997834295158</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="B23" s="2" t="n">
+        <v>0.01830102797345684</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0.01830102771549491</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>2.579619295950408e-10</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-0.01830102797345684</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-0.01830102789313059</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-8.032624565501578e-11</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>2.579619295950408e-10</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1.910453648501145e-10</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9999998043209929</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>h from (bohr)</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>h to (bohr)</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>log-log slope</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-0.6110699539010074</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>energy noise (1/h), step too small</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1.042049735063786e-05</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>near the optimum</t>
-        </is>
-      </c>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="1" t="n"/>
+      <c r="K25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>0.0001</v>
+        <v>1e-05</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.0005</v>
+        <v>2e-05</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.815129459441813</v>
+        <v>-2.844406367353519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>truncation (h^2), step too large</t>
+          <t>energy noise (1/h), step too small</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.8677530470919746</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>near the optimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1.943820599305689</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1.906843821940805</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>0.0005</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>1.99786007876487</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2.000886600922158</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ccpvdz</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bond length (Angstrom)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ncas</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>nelecas</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>act_list (1-based)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[3, 4, 7, 10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>act_list character</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3: sigma(F2s); 4: sigma(F2pz-Li); 7: sigma*(Li3s); 10: sigma*(Li3pz).  Default window would be [5,6,7,8], whose MOs 5 and 6 are the F 2p pi lone pairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>reference energy (Eh)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-106.9430017857996</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>net force norm (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>torque (Eh)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.939466935556067e-16</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>atom</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>analytic z (Eh/bohr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>step_bohr</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>analytic z Li (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>numerical z Li (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>diff Li (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>analytic z F (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>numerical z F (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>diff F (Eh/bohr)</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>max_abs_error_Eh_per_bohr</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>rms_error_Eh_per_bohr</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>min_active_overlap</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>best_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0.03524757631367947</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-1.330884948913535e-07</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-0.0352475763989446</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1.331737706777858e-07</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1.331737706777858e-07</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1.331311396123862e-07</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9999783088580678</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0.03524747619110258</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-3.296591799539783e-08</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-0.03524747629057856</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>3.306540463654528e-08</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>3.306540463654528e-08</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>3.301569878904401e-08</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9999891630406625</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>0.03524744812466452</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>-4.899479932873874e-09</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-0.03524744823124593</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>5.006072001378925e-09</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>5.006072001378925e-09</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>4.953062713898532e-09</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9999956672822105</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0.0352474452114393</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>-1.986254716257463e-09</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-0.03524744506933075</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1.844156827246479e-09</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1.986254716257463e-09</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1.916523180310483e-09</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9999978339853591</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0.03524744329297391</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-6.778932970519236e-11</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-0.03524744428773374</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1.062559817910369e-09</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1.062559817910369e-09</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7.528707591146026e-10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9999989170787364</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0.0352474376796863</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>5.545498282799599e-09</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-0.0352474366138722</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-6.611301728298713e-09</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>6.611301728298713e-09</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>6.10171540417688e-09</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.999999566852147</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.03524744322518458</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0.03524744371929955</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>-4.941149711612525e-10</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-0.03524744322517392</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-0.03524744442984229</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1.204668365062389e-09</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1.204668365062389e-09</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>9.206995912097971e-10</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9999997834295155</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>h from (bohr)</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>h to (bohr)</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>log-log slope</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="1" t="n"/>
+      <c r="K25" s="1" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2.456298318819181</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>2e-05</v>
+      </c>
       <c r="B27" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-1.995108740727974</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>energy noise (1/h), step too small</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.9025065836266678</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>near the optimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1.333628396001681</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2.06030238773366</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>2.007350634846032</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C31" s="3" t="n">
+        <v>2.009915501778255</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>truncation (h^2), step too large</t>
         </is>
@@ -3004,7 +3788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3013,7 +3797,7 @@
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -3115,7 +3899,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.371880883511039e-14</v>
+        <v>7.105427357601002e-14</v>
       </c>
     </row>
     <row r="10">
@@ -3125,7 +3909,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.027990320564627e-15</v>
+        <v>8.728013272129846e-16</v>
       </c>
     </row>
     <row r="11"/>
@@ -3148,7 +3932,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.3397175965682662</v>
       </c>
     </row>
     <row r="14">
@@ -3158,7 +3942,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.3397175965681951</v>
       </c>
     </row>
     <row r="15"/>
@@ -3224,31 +4008,31 @@
         <v>0.001</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.3397175965682662</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.3397178301725035</v>
+        <v>0.3397178302861903</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-2.336066735608711e-07</v>
+        <v>-2.337179241251874e-07</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.3397175965681951</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.3397178302861903</v>
+        <v>-0.3397178300019732</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2.337204341174015e-07</v>
+        <v>2.33433778085157e-07</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2.337204341174015e-07</v>
+        <v>2.337179241251874e-07</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2.336635607622656e-07</v>
+        <v>2.335758943132801e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9998816702115469</v>
+        <v>0.9998816702115806</v>
       </c>
       <c r="K17" t="inlineStr"/>
     </row>
@@ -3257,226 +4041,324 @@
         <v>0.0005</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.3397175965682662</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.3397176548673997</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-5.830156979413914e-08</v>
+        <v>-5.82991335207339e-08</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.3397175965681951</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-0.3397176548105563</v>
+        <v>-0.3397176552653036</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5.824480009408717e-08</v>
+        <v>5.869710850703314e-08</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>5.830156979413914e-08</v>
+        <v>5.869710850703314e-08</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5.82731918572385e-08</v>
+        <v>5.84984594513171e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9999408486791898</v>
+        <v>0.9999408486792066</v>
       </c>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.3397175965682662</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.3397175987629453</v>
+        <v>0.3397176055841555</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-2.19711537852163e-09</v>
+        <v>-9.015889368413355e-09</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.3397175965681951</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.3397175998998136</v>
+        <v>-0.3397176050157213</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3.334057474546626e-09</v>
+        <v>8.44752623407885e-09</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3.334057474546626e-09</v>
+        <v>9.015889368413355e-09</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2.823407093399433e-09</v>
+        <v>8.736331054250387e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9999881719069121</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>0.9999763427284053</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.3397175965658299</v>
+        <v>0.3397175965682662</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.3397175959207743</v>
+        <v>0.3397175981945111</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6.450555645187706e-10</v>
+        <v>-1.626244916508313e-09</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.3397175965657562</v>
+        <v>-0.3397175965681951</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.3397176004682478</v>
+        <v>-0.339717597910294</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3.902491663154706e-09</v>
+        <v>1.342098876477849e-09</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.902491663154706e-09</v>
+        <v>1.626244916508313e-09</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.796921330884068e-09</v>
+        <v>1.490956391500474e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9999940860891267</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>0.9999881719069152</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0.339717594783906</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1.784360215140168e-09</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-0.3397175987629453</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2.194750159389969e-09</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>2.194750159389969e-09</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>2.00010870198564e-09</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9999940860891284</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0.3397176001840307</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>-3.615764521125442e-09</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-0.3397175944996888</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-2.068506310681784e-09</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>3.615764521125442e-09</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>2.945545062425617e-09</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9999976344682114</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>1e-05</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>0.3397175965658299</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0.3397176243424837</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>-2.777665381037409e-08</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-0.3397175965657562</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-0.339717607289458</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1.072370187094052e-08</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>2.777665381037409e-08</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>2.10539815559692e-08</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9999988172395315</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="B23" s="2" t="n">
+        <v>0.3397175965682662</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0.3397175873942614</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9.174004722556361e-09</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-0.3397175965681951</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-0.3397175902364324</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-6.331762725242385e-09</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>9.174004722556361e-09</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>7.8820549940436e-09</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9999988172395318</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>h from (bohr)</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>h to (bohr)</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>log-log slope</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-1.219419913372564</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>energy noise (1/h), step too small</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>-0.2271165755857938</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>near the optimum</t>
-        </is>
-      </c>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="1" t="n"/>
+      <c r="K25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>0.0001</v>
+        <v>1e-05</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.0005</v>
+        <v>2e-05</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.77791201135131</v>
+        <v>-1.343250925668602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>truncation (h^2), step too large</t>
+          <t>energy noise (1/h), step too small</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.5448435569905569</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>energy noise (1/h), step too small</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-0.4325121718934703</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>near the optimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2.470925265472206</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>0.0005</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="C30" s="3" t="n">
+        <v>2.044549721557238</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>truncation (h^2), step too large</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>2.003177239862664</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C31" s="3" t="n">
+        <v>1.993407039246676</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>truncation (h^2), step too large</t>
         </is>
